--- a/Reference_Data_CFI.xlsx
+++ b/Reference_Data_CFI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\dcamacho\dev\ProjectData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FF13917-A4D1-45A4-A601-511E6ED6DBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6EB030-DA54-4500-8D0E-07EBF970C255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fluid" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="343">
   <si>
     <t>Unit</t>
   </si>
@@ -970,9 +970,6 @@
     <t>code</t>
   </si>
   <si>
-    <t>Class</t>
-  </si>
-  <si>
     <t>Role</t>
   </si>
   <si>
@@ -1030,9 +1027,6 @@
     <t>Instrument</t>
   </si>
   <si>
-    <t>\d{0,2}[A-Z]{2,4}-?\d{3,6}[A-Z]?</t>
-  </si>
-  <si>
     <t>Optional unit + ISA function letters (2-4) + loop number, optional suffix (e.g. PT1401, 14FIC-2201A, LT-220701). STARTER PATTERN — confirm against the project instrument tag register.</t>
   </si>
   <si>
@@ -1085,6 +1079,15 @@
   </si>
   <si>
     <t>Cold Conservation (STARTER — include only if used on this project)</t>
+  </si>
+  <si>
+    <t>\d{2}-?[A-Z]{1,4}-?\d{3,6}[A-Z]?</t>
+  </si>
+  <si>
+    <t>FluidCode</t>
+  </si>
+  <si>
+    <t>ComponentClass</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1481,7 @@
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>341</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>34</v>
@@ -2390,21 +2393,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
         <v>303</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B2" t="s">
         <v>306</v>
-      </c>
-      <c r="B2" t="s">
-        <v>307</v>
       </c>
       <c r="C2" t="s">
         <v>290</v>
@@ -2412,10 +2415,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C3" t="s">
         <v>290</v>
@@ -2423,10 +2426,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C4" t="s">
         <v>290</v>
@@ -2434,10 +2437,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" t="s">
         <v>310</v>
-      </c>
-      <c r="B5" t="s">
-        <v>311</v>
       </c>
       <c r="C5" t="s">
         <v>290</v>
@@ -2445,10 +2448,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" t="s">
         <v>312</v>
-      </c>
-      <c r="B6" t="s">
-        <v>313</v>
       </c>
       <c r="C6" t="s">
         <v>290</v>
@@ -2456,10 +2459,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" t="s">
         <v>314</v>
-      </c>
-      <c r="B7" t="s">
-        <v>315</v>
       </c>
       <c r="C7" t="s">
         <v>290</v>
@@ -2467,10 +2470,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C8" t="s">
         <v>290</v>
@@ -2478,7 +2481,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C9" t="s">
         <v>282</v>
@@ -2504,7 +2507,7 @@
         <v>270</v>
       </c>
       <c r="B1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C1" t="s">
         <v>138</v>
@@ -2512,46 +2515,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" t="s">
         <v>319</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>320</v>
-      </c>
-      <c r="C2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" t="s">
         <v>322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C3" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" t="s">
         <v>325</v>
-      </c>
-      <c r="B4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" t="s">
         <v>328</v>
-      </c>
-      <c r="B5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C5" t="s">
-        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -2581,47 +2584,47 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
